--- a/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
+++ b/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
@@ -62338,13 +62338,13 @@
         <v>12</v>
       </c>
       <c r="T128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U128" t="n">
         <v>23</v>
       </c>
       <c r="V128" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W128" t="n">
         <v>13</v>
@@ -62353,10 +62353,10 @@
         <v>16</v>
       </c>
       <c r="Y128" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Z128" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
@@ -62519,10 +62519,10 @@
         <v>2.64</v>
       </c>
       <c r="CA128" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="CB128" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="CC128" t="n">
         <v>0</v>
@@ -63654,76 +63654,84 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="EA130" t="inlineStr"/>
+      <c r="EA130" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
       <c r="EB130" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EC130" t="inlineStr">
         <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="ED130" t="inlineStr"/>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="ED130" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
       <c r="EE130" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="EF130" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EG130" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="EH130" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EI130" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="EJ130" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EK130" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EL130" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EM130" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EN130" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="EO130" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="EP130" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.91</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
+++ b/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
@@ -65713,10 +65713,10 @@
         <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S135" t="n">
         <v>20</v>
@@ -65725,10 +65725,10 @@
         <v>7</v>
       </c>
       <c r="U135" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V135" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W135" t="n">
         <v>15</v>
@@ -65900,10 +65900,10 @@
         <v>77</v>
       </c>
       <c r="BZ135" t="n">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="CA135" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="CB135" t="n">
         <v>3.73</v>
@@ -66225,10 +66225,10 @@
         <v>12</v>
       </c>
       <c r="Y136" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Z136" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
@@ -68139,13 +68139,13 @@
         <v>2</v>
       </c>
       <c r="S140" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T140" t="n">
         <v>7</v>
       </c>
       <c r="U140" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="V140" t="n">
         <v>9</v>
@@ -68320,13 +68320,13 @@
         <v>96</v>
       </c>
       <c r="BZ140" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="CA140" t="n">
         <v>1.12</v>
       </c>
       <c r="CB140" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="CC140" t="n">
         <v>0</v>

--- a/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
+++ b/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
@@ -73648,7 +73648,7 @@
         <v>1</v>
       </c>
       <c r="CX151" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CY151" t="n">
         <v>7</v>

--- a/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
+++ b/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
@@ -73879,10 +73879,10 @@
         <v>7</v>
       </c>
       <c r="W152" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X152" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y152" t="n">
         <v>43</v>
@@ -77249,13 +77249,13 @@
         <v>0</v>
       </c>
       <c r="Q159" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R159" t="n">
         <v>7</v>
       </c>
       <c r="S159" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T159" t="n">
         <v>8</v>
@@ -77436,13 +77436,13 @@
         <v>77</v>
       </c>
       <c r="BZ159" t="n">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="CA159" t="n">
         <v>1.75</v>
       </c>
       <c r="CB159" t="n">
-        <v>3.96</v>
+        <v>4.03</v>
       </c>
       <c r="CC159" t="n">
         <v>0</v>

--- a/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
+++ b/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
@@ -84701,7 +84701,7 @@
         <v>26</v>
       </c>
       <c r="CS174" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CT174" t="n">
         <v>1</v>
@@ -85916,7 +85916,7 @@
         <v>4</v>
       </c>
       <c r="R177" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S177" t="n">
         <v>11</v>
@@ -85928,7 +85928,7 @@
         <v>15</v>
       </c>
       <c r="V177" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W177" t="n">
         <v>19</v>
@@ -86043,28 +86043,28 @@
         <v>-1</v>
       </c>
       <c r="BG177" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH177" t="n">
         <v>1</v>
       </c>
       <c r="BI177" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BJ177" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BK177" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BL177" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM177" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BN177" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BO177" t="n">
         <v>2</v>
@@ -86103,10 +86103,10 @@
         <v>1.64</v>
       </c>
       <c r="CA177" t="n">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="CB177" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="CC177" t="n">
         <v>0</v>
@@ -86139,10 +86139,10 @@
         <v>0</v>
       </c>
       <c r="CM177" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CN177" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO177" t="n">
         <v>0</v>
@@ -86163,7 +86163,7 @@
         <v>1</v>
       </c>
       <c r="CU177" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CV177" t="n">
         <v>19</v>

--- a/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
+++ b/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
@@ -20904,7 +20904,7 @@
         <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>-1</v>
+        <v>8884</v>
       </c>
       <c r="BG42" t="n">
         <v>2</v>
@@ -21392,7 +21392,7 @@
         <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>-1</v>
+        <v>14423</v>
       </c>
       <c r="BG43" t="n">
         <v>2</v>
@@ -21880,7 +21880,7 @@
         <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>-1</v>
+        <v>10314</v>
       </c>
       <c r="BG44" t="n">
         <v>2</v>
@@ -22352,7 +22352,7 @@
         <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>-1</v>
+        <v>7126</v>
       </c>
       <c r="BG45" t="n">
         <v>2</v>
@@ -22840,7 +22840,7 @@
         <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>-1</v>
+        <v>4086</v>
       </c>
       <c r="BG46" t="n">
         <v>2</v>
@@ -23328,7 +23328,7 @@
         <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>-1</v>
+        <v>7119</v>
       </c>
       <c r="BG47" t="n">
         <v>2</v>
@@ -23804,7 +23804,7 @@
         <v>0</v>
       </c>
       <c r="BF48" t="n">
-        <v>-1</v>
+        <v>5402</v>
       </c>
       <c r="BG48" t="n">
         <v>2</v>
@@ -24292,7 +24292,7 @@
         <v>0</v>
       </c>
       <c r="BF49" t="n">
-        <v>-1</v>
+        <v>13845</v>
       </c>
       <c r="BG49" t="n">
         <v>2</v>
@@ -24780,7 +24780,7 @@
         <v>0</v>
       </c>
       <c r="BF50" t="n">
-        <v>-1</v>
+        <v>11259</v>
       </c>
       <c r="BG50" t="n">
         <v>2</v>
@@ -25268,7 +25268,7 @@
         <v>0</v>
       </c>
       <c r="BF51" t="n">
-        <v>-1</v>
+        <v>7069</v>
       </c>
       <c r="BG51" t="n">
         <v>2</v>
@@ -25756,7 +25756,7 @@
         <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>-1</v>
+        <v>9933</v>
       </c>
       <c r="BG52" t="n">
         <v>2</v>
@@ -26244,7 +26244,7 @@
         <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>-1</v>
+        <v>2126</v>
       </c>
       <c r="BG53" t="n">
         <v>2</v>
@@ -26732,7 +26732,7 @@
         <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>-1</v>
+        <v>7374</v>
       </c>
       <c r="BG54" t="n">
         <v>2</v>
@@ -27212,7 +27212,7 @@
         <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>-1</v>
+        <v>3814</v>
       </c>
       <c r="BG55" t="n">
         <v>2</v>
@@ -27684,7 +27684,7 @@
         <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>-1</v>
+        <v>8632</v>
       </c>
       <c r="BG56" t="n">
         <v>2</v>
@@ -28172,7 +28172,7 @@
         <v>0</v>
       </c>
       <c r="BF57" t="n">
-        <v>-1</v>
+        <v>31933</v>
       </c>
       <c r="BG57" t="n">
         <v>2</v>
@@ -28648,7 +28648,7 @@
         <v>0</v>
       </c>
       <c r="BF58" t="n">
-        <v>-1</v>
+        <v>3044</v>
       </c>
       <c r="BG58" t="n">
         <v>2</v>
@@ -29136,7 +29136,7 @@
         <v>0</v>
       </c>
       <c r="BF59" t="n">
-        <v>-1</v>
+        <v>5263</v>
       </c>
       <c r="BG59" t="n">
         <v>2</v>
@@ -29624,7 +29624,7 @@
         <v>0</v>
       </c>
       <c r="BF60" t="n">
-        <v>-1</v>
+        <v>22495</v>
       </c>
       <c r="BG60" t="n">
         <v>2</v>
@@ -30096,7 +30096,7 @@
         <v>0</v>
       </c>
       <c r="BF61" t="n">
-        <v>-1</v>
+        <v>6014</v>
       </c>
       <c r="BG61" t="n">
         <v>2</v>
@@ -30584,7 +30584,7 @@
         <v>0</v>
       </c>
       <c r="BF62" t="n">
-        <v>-1</v>
+        <v>7559</v>
       </c>
       <c r="BG62" t="n">
         <v>2</v>
@@ -31056,7 +31056,7 @@
         <v>0</v>
       </c>
       <c r="BF63" t="n">
-        <v>-1</v>
+        <v>7526</v>
       </c>
       <c r="BG63" t="n">
         <v>-1</v>
@@ -31544,7 +31544,7 @@
         <v>0</v>
       </c>
       <c r="BF64" t="n">
-        <v>-1</v>
+        <v>9717</v>
       </c>
       <c r="BG64" t="n">
         <v>2</v>
@@ -32032,7 +32032,7 @@
         <v>0</v>
       </c>
       <c r="BF65" t="n">
-        <v>-1</v>
+        <v>9913</v>
       </c>
       <c r="BG65" t="n">
         <v>2</v>
@@ -32520,7 +32520,7 @@
         <v>0</v>
       </c>
       <c r="BF66" t="n">
-        <v>-1</v>
+        <v>9392</v>
       </c>
       <c r="BG66" t="n">
         <v>2</v>
@@ -33008,7 +33008,7 @@
         <v>0</v>
       </c>
       <c r="BF67" t="n">
-        <v>-1</v>
+        <v>11703</v>
       </c>
       <c r="BG67" t="n">
         <v>2</v>
@@ -33496,7 +33496,7 @@
         <v>0</v>
       </c>
       <c r="BF68" t="n">
-        <v>-1</v>
+        <v>3439</v>
       </c>
       <c r="BG68" t="n">
         <v>2</v>
@@ -33960,7 +33960,7 @@
         <v>0</v>
       </c>
       <c r="BF69" t="n">
-        <v>-1</v>
+        <v>2616</v>
       </c>
       <c r="BG69" t="n">
         <v>2</v>
@@ -34440,7 +34440,7 @@
         <v>0</v>
       </c>
       <c r="BF70" t="n">
-        <v>-1</v>
+        <v>23039</v>
       </c>
       <c r="BG70" t="n">
         <v>2</v>
@@ -34928,7 +34928,7 @@
         <v>0</v>
       </c>
       <c r="BF71" t="n">
-        <v>-1</v>
+        <v>9666</v>
       </c>
       <c r="BG71" t="n">
         <v>2</v>
@@ -35408,7 +35408,7 @@
         <v>0</v>
       </c>
       <c r="BF72" t="n">
-        <v>-1</v>
+        <v>5535</v>
       </c>
       <c r="BG72" t="n">
         <v>2</v>
@@ -35864,7 +35864,7 @@
         <v>0</v>
       </c>
       <c r="BF73" t="n">
-        <v>-1</v>
+        <v>10163</v>
       </c>
       <c r="BG73" t="n">
         <v>2</v>
@@ -36352,7 +36352,7 @@
         <v>0</v>
       </c>
       <c r="BF74" t="n">
-        <v>-1</v>
+        <v>8846</v>
       </c>
       <c r="BG74" t="n">
         <v>2</v>
@@ -36840,7 +36840,7 @@
         <v>0</v>
       </c>
       <c r="BF75" t="n">
-        <v>-1</v>
+        <v>6982</v>
       </c>
       <c r="BG75" t="n">
         <v>2</v>
@@ -37328,7 +37328,7 @@
         <v>0</v>
       </c>
       <c r="BF76" t="n">
-        <v>-1</v>
+        <v>7194</v>
       </c>
       <c r="BG76" t="n">
         <v>2</v>
@@ -37664,7 +37664,7 @@
         <v>2</v>
       </c>
       <c r="N77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -37800,7 +37800,7 @@
         <v>0</v>
       </c>
       <c r="BF77" t="n">
-        <v>-1</v>
+        <v>5280</v>
       </c>
       <c r="BG77" t="n">
         <v>2</v>
@@ -37836,13 +37836,13 @@
         <v>2</v>
       </c>
       <c r="BR77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS77" t="n">
         <v>0</v>
       </c>
       <c r="BT77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BU77" t="n">
         <v>1</v>
@@ -38268,7 +38268,7 @@
         <v>0</v>
       </c>
       <c r="BF78" t="n">
-        <v>-1</v>
+        <v>8369</v>
       </c>
       <c r="BG78" t="n">
         <v>2</v>
@@ -38756,7 +38756,7 @@
         <v>0</v>
       </c>
       <c r="BF79" t="n">
-        <v>-1</v>
+        <v>32922</v>
       </c>
       <c r="BG79" t="n">
         <v>2</v>
@@ -39216,7 +39216,7 @@
         <v>0</v>
       </c>
       <c r="BF80" t="n">
-        <v>-1</v>
+        <v>6640</v>
       </c>
       <c r="BG80" t="n">
         <v>2</v>
@@ -39688,7 +39688,7 @@
         <v>0</v>
       </c>
       <c r="BF81" t="n">
-        <v>-1</v>
+        <v>7953</v>
       </c>
       <c r="BG81" t="n">
         <v>2</v>
@@ -40176,7 +40176,7 @@
         <v>0</v>
       </c>
       <c r="BF82" t="n">
-        <v>-1</v>
+        <v>11879</v>
       </c>
       <c r="BG82" t="n">
         <v>2</v>
@@ -40664,7 +40664,7 @@
         <v>0</v>
       </c>
       <c r="BF83" t="n">
-        <v>-1</v>
+        <v>4075</v>
       </c>
       <c r="BG83" t="n">
         <v>2</v>
@@ -41152,7 +41152,7 @@
         <v>0</v>
       </c>
       <c r="BF84" t="n">
-        <v>-1</v>
+        <v>9306</v>
       </c>
       <c r="BG84" t="n">
         <v>2</v>
@@ -41632,7 +41632,7 @@
         <v>0</v>
       </c>
       <c r="BF85" t="n">
-        <v>-1</v>
+        <v>2369</v>
       </c>
       <c r="BG85" t="n">
         <v>2</v>
@@ -42120,7 +42120,7 @@
         <v>0</v>
       </c>
       <c r="BF86" t="n">
-        <v>-1</v>
+        <v>5513</v>
       </c>
       <c r="BG86" t="n">
         <v>2</v>
@@ -42608,7 +42608,7 @@
         <v>0</v>
       </c>
       <c r="BF87" t="n">
-        <v>-1</v>
+        <v>22675</v>
       </c>
       <c r="BG87" t="n">
         <v>2</v>
@@ -43096,7 +43096,7 @@
         <v>0</v>
       </c>
       <c r="BF88" t="n">
-        <v>-1</v>
+        <v>2498</v>
       </c>
       <c r="BG88" t="n">
         <v>2</v>
@@ -43568,7 +43568,7 @@
         <v>0</v>
       </c>
       <c r="BF89" t="n">
-        <v>-1</v>
+        <v>8400</v>
       </c>
       <c r="BG89" t="n">
         <v>2</v>
@@ -44056,7 +44056,7 @@
         <v>0</v>
       </c>
       <c r="BF90" t="n">
-        <v>-1</v>
+        <v>7357</v>
       </c>
       <c r="BG90" t="n">
         <v>2</v>
@@ -44536,7 +44536,7 @@
         <v>0</v>
       </c>
       <c r="BF91" t="n">
-        <v>-1</v>
+        <v>9866</v>
       </c>
       <c r="BG91" t="n">
         <v>2</v>
@@ -45008,7 +45008,7 @@
         <v>0</v>
       </c>
       <c r="BF92" t="n">
-        <v>-1</v>
+        <v>14719</v>
       </c>
       <c r="BG92" t="n">
         <v>2</v>
@@ -45496,7 +45496,7 @@
         <v>0</v>
       </c>
       <c r="BF93" t="n">
-        <v>-1</v>
+        <v>26679</v>
       </c>
       <c r="BG93" t="n">
         <v>2</v>
@@ -45972,7 +45972,7 @@
         <v>0</v>
       </c>
       <c r="BF94" t="n">
-        <v>-1</v>
+        <v>5947</v>
       </c>
       <c r="BG94" t="n">
         <v>2</v>
@@ -46460,7 +46460,7 @@
         <v>0</v>
       </c>
       <c r="BF95" t="n">
-        <v>-1</v>
+        <v>9075</v>
       </c>
       <c r="BG95" t="n">
         <v>2</v>
@@ -46948,7 +46948,7 @@
         <v>0</v>
       </c>
       <c r="BF96" t="n">
-        <v>-1</v>
+        <v>7987</v>
       </c>
       <c r="BG96" t="n">
         <v>2</v>
@@ -47436,7 +47436,7 @@
         <v>0</v>
       </c>
       <c r="BF97" t="n">
-        <v>-1</v>
+        <v>10359</v>
       </c>
       <c r="BG97" t="n">
         <v>2</v>
@@ -47924,7 +47924,7 @@
         <v>0</v>
       </c>
       <c r="BF98" t="n">
-        <v>-1</v>
+        <v>7117</v>
       </c>
       <c r="BG98" t="n">
         <v>2</v>
@@ -48412,7 +48412,7 @@
         <v>0</v>
       </c>
       <c r="BF99" t="n">
-        <v>-1</v>
+        <v>7747</v>
       </c>
       <c r="BG99" t="n">
         <v>2</v>
@@ -48900,7 +48900,7 @@
         <v>0</v>
       </c>
       <c r="BF100" t="n">
-        <v>-1</v>
+        <v>8143</v>
       </c>
       <c r="BG100" t="n">
         <v>2</v>
@@ -49249,10 +49249,10 @@
         <v>8</v>
       </c>
       <c r="M101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -49301,10 +49301,10 @@
         </is>
       </c>
       <c r="AC101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE101" t="n">
         <v>1.93</v>
@@ -49388,7 +49388,7 @@
         <v>0</v>
       </c>
       <c r="BF101" t="n">
-        <v>-1</v>
+        <v>9428</v>
       </c>
       <c r="BG101" t="n">
         <v>2</v>
@@ -49418,19 +49418,19 @@
         <v>1</v>
       </c>
       <c r="BP101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT101" t="n">
         <v>3</v>
-      </c>
-      <c r="BR101" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS101" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT101" t="n">
-        <v>5</v>
       </c>
       <c r="BU101" t="n">
         <v>1</v>
@@ -49876,7 +49876,7 @@
         <v>0</v>
       </c>
       <c r="BF102" t="n">
-        <v>-1</v>
+        <v>2606</v>
       </c>
       <c r="BG102" t="n">
         <v>2</v>
@@ -50225,10 +50225,10 @@
         <v>9</v>
       </c>
       <c r="M103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -50277,10 +50277,10 @@
         </is>
       </c>
       <c r="AC103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE103" t="n">
         <v>2.43</v>
@@ -50364,7 +50364,7 @@
         <v>0</v>
       </c>
       <c r="BF103" t="n">
-        <v>-1</v>
+        <v>7078</v>
       </c>
       <c r="BG103" t="n">
         <v>2</v>
@@ -50397,16 +50397,16 @@
         <v>0</v>
       </c>
       <c r="BQ103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS103" t="n">
         <v>0</v>
       </c>
       <c r="BT103" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BU103" t="n">
         <v>1</v>
@@ -50852,7 +50852,7 @@
         <v>0</v>
       </c>
       <c r="BF104" t="n">
-        <v>-1</v>
+        <v>2528</v>
       </c>
       <c r="BG104" t="n">
         <v>2</v>
@@ -51324,7 +51324,7 @@
         <v>0</v>
       </c>
       <c r="BF105" t="n">
-        <v>-1</v>
+        <v>27077</v>
       </c>
       <c r="BG105" t="n">
         <v>2</v>
@@ -51800,7 +51800,7 @@
         <v>0</v>
       </c>
       <c r="BF106" t="n">
-        <v>-1</v>
+        <v>9271</v>
       </c>
       <c r="BG106" t="n">
         <v>2</v>
@@ -52288,7 +52288,7 @@
         <v>0</v>
       </c>
       <c r="BF107" t="n">
-        <v>-1</v>
+        <v>9805</v>
       </c>
       <c r="BG107" t="n">
         <v>2</v>
@@ -52776,7 +52776,7 @@
         <v>0</v>
       </c>
       <c r="BF108" t="n">
-        <v>-1</v>
+        <v>8655</v>
       </c>
       <c r="BG108" t="n">
         <v>2</v>
@@ -53264,7 +53264,7 @@
         <v>0</v>
       </c>
       <c r="BF109" t="n">
-        <v>-1</v>
+        <v>4962</v>
       </c>
       <c r="BG109" t="n">
         <v>2</v>
@@ -53752,7 +53752,7 @@
         <v>0</v>
       </c>
       <c r="BF110" t="n">
-        <v>-1</v>
+        <v>22321</v>
       </c>
       <c r="BG110" t="n">
         <v>2</v>
@@ -54224,7 +54224,7 @@
         <v>0</v>
       </c>
       <c r="BF111" t="n">
-        <v>-1</v>
+        <v>8836</v>
       </c>
       <c r="BG111" t="n">
         <v>2</v>
@@ -54712,7 +54712,7 @@
         <v>0</v>
       </c>
       <c r="BF112" t="n">
-        <v>-1</v>
+        <v>3022</v>
       </c>
       <c r="BG112" t="n">
         <v>2</v>
@@ -55184,7 +55184,7 @@
         <v>0</v>
       </c>
       <c r="BF113" t="n">
-        <v>-1</v>
+        <v>8096</v>
       </c>
       <c r="BG113" t="n">
         <v>2</v>
@@ -55656,7 +55656,7 @@
         <v>0</v>
       </c>
       <c r="BF114" t="n">
-        <v>-1</v>
+        <v>6816</v>
       </c>
       <c r="BG114" t="n">
         <v>2</v>
@@ -56128,7 +56128,7 @@
         <v>0</v>
       </c>
       <c r="BF115" t="n">
-        <v>-1</v>
+        <v>8239</v>
       </c>
       <c r="BG115" t="n">
         <v>2</v>
@@ -56616,7 +56616,7 @@
         <v>0</v>
       </c>
       <c r="BF116" t="n">
-        <v>-1</v>
+        <v>11412</v>
       </c>
       <c r="BG116" t="n">
         <v>2</v>
@@ -57104,7 +57104,7 @@
         <v>0</v>
       </c>
       <c r="BF117" t="n">
-        <v>-1</v>
+        <v>3893</v>
       </c>
       <c r="BG117" t="n">
         <v>2</v>
@@ -57592,7 +57592,7 @@
         <v>0</v>
       </c>
       <c r="BF118" t="n">
-        <v>-1</v>
+        <v>9001</v>
       </c>
       <c r="BG118" t="n">
         <v>2</v>
@@ -58080,7 +58080,7 @@
         <v>0</v>
       </c>
       <c r="BF119" t="n">
-        <v>-1</v>
+        <v>13225</v>
       </c>
       <c r="BG119" t="n">
         <v>2</v>
@@ -58568,7 +58568,7 @@
         <v>0</v>
       </c>
       <c r="BF120" t="n">
-        <v>-1</v>
+        <v>7372</v>
       </c>
       <c r="BG120" t="n">
         <v>2</v>
@@ -59528,7 +59528,7 @@
         <v>0</v>
       </c>
       <c r="BF122" t="n">
-        <v>-1</v>
+        <v>2956</v>
       </c>
       <c r="BG122" t="n">
         <v>2</v>
@@ -60016,7 +60016,7 @@
         <v>0</v>
       </c>
       <c r="BF123" t="n">
-        <v>-1</v>
+        <v>3351</v>
       </c>
       <c r="BG123" t="n">
         <v>2</v>
@@ -60504,7 +60504,7 @@
         <v>0</v>
       </c>
       <c r="BF124" t="n">
-        <v>-1</v>
+        <v>8000</v>
       </c>
       <c r="BG124" t="n">
         <v>2</v>
@@ -60853,7 +60853,7 @@
         <v>14</v>
       </c>
       <c r="M125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N125" t="n">
         <v>3</v>
@@ -60905,7 +60905,7 @@
         </is>
       </c>
       <c r="AC125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD125" t="n">
         <v>3</v>
@@ -60992,7 +60992,7 @@
         <v>0</v>
       </c>
       <c r="BF125" t="n">
-        <v>-1</v>
+        <v>8027</v>
       </c>
       <c r="BG125" t="n">
         <v>2</v>
@@ -61025,7 +61025,7 @@
         <v>1</v>
       </c>
       <c r="BQ125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR125" t="n">
         <v>2</v>
@@ -61034,7 +61034,7 @@
         <v>1</v>
       </c>
       <c r="BT125" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BU125" t="n">
         <v>1</v>
@@ -61480,7 +61480,7 @@
         <v>0</v>
       </c>
       <c r="BF126" t="n">
-        <v>-1</v>
+        <v>10816</v>
       </c>
       <c r="BG126" t="n">
         <v>2</v>
@@ -61968,7 +61968,7 @@
         <v>0</v>
       </c>
       <c r="BF127" t="n">
-        <v>-1</v>
+        <v>7901</v>
       </c>
       <c r="BG127" t="n">
         <v>2</v>
@@ -62456,7 +62456,7 @@
         <v>0</v>
       </c>
       <c r="BF128" t="n">
-        <v>-1</v>
+        <v>10890</v>
       </c>
       <c r="BG128" t="n">
         <v>2</v>
@@ -62944,7 +62944,7 @@
         <v>0</v>
       </c>
       <c r="BF129" t="n">
-        <v>-1</v>
+        <v>7777</v>
       </c>
       <c r="BG129" t="n">
         <v>2</v>
@@ -63432,7 +63432,7 @@
         <v>0</v>
       </c>
       <c r="BF130" t="n">
-        <v>-1</v>
+        <v>21239</v>
       </c>
       <c r="BG130" t="n">
         <v>2</v>
@@ -63920,7 +63920,7 @@
         <v>0</v>
       </c>
       <c r="BF131" t="n">
-        <v>-1</v>
+        <v>13422</v>
       </c>
       <c r="BG131" t="n">
         <v>2</v>
@@ -64392,7 +64392,7 @@
         <v>0</v>
       </c>
       <c r="BF132" t="n">
-        <v>-1</v>
+        <v>7363</v>
       </c>
       <c r="BG132" t="n">
         <v>2</v>
@@ -64880,7 +64880,7 @@
         <v>0</v>
       </c>
       <c r="BF133" t="n">
-        <v>-1</v>
+        <v>6784</v>
       </c>
       <c r="BG133" t="n">
         <v>2</v>
@@ -65368,7 +65368,7 @@
         <v>0</v>
       </c>
       <c r="BF134" t="n">
-        <v>-1</v>
+        <v>6000</v>
       </c>
       <c r="BG134" t="n">
         <v>2</v>
@@ -65856,7 +65856,7 @@
         <v>0</v>
       </c>
       <c r="BF135" t="n">
-        <v>-1</v>
+        <v>7850</v>
       </c>
       <c r="BG135" t="n">
         <v>2</v>
@@ -66328,7 +66328,7 @@
         <v>0</v>
       </c>
       <c r="BF136" t="n">
-        <v>-1</v>
+        <v>3725</v>
       </c>
       <c r="BG136" t="n">
         <v>2</v>
@@ -66816,7 +66816,7 @@
         <v>0</v>
       </c>
       <c r="BF137" t="n">
-        <v>-1</v>
+        <v>7691</v>
       </c>
       <c r="BG137" t="n">
         <v>2</v>
@@ -67304,7 +67304,7 @@
         <v>0</v>
       </c>
       <c r="BF138" t="n">
-        <v>-1</v>
+        <v>21834</v>
       </c>
       <c r="BG138" t="n">
         <v>2</v>
@@ -67780,7 +67780,7 @@
         <v>0</v>
       </c>
       <c r="BF139" t="n">
-        <v>-1</v>
+        <v>3896</v>
       </c>
       <c r="BG139" t="n">
         <v>2</v>
@@ -68260,7 +68260,7 @@
         <v>0</v>
       </c>
       <c r="BF140" t="n">
-        <v>-1</v>
+        <v>8774</v>
       </c>
       <c r="BG140" t="n">
         <v>2</v>
@@ -68716,7 +68716,7 @@
         <v>0</v>
       </c>
       <c r="BF141" t="n">
-        <v>-1</v>
+        <v>3501</v>
       </c>
       <c r="BG141" t="n">
         <v>2</v>
@@ -69204,7 +69204,7 @@
         <v>0</v>
       </c>
       <c r="BF142" t="n">
-        <v>-1</v>
+        <v>8000</v>
       </c>
       <c r="BG142" t="n">
         <v>2</v>
@@ -69676,7 +69676,7 @@
         <v>0</v>
       </c>
       <c r="BF143" t="n">
-        <v>-1</v>
+        <v>22707</v>
       </c>
       <c r="BG143" t="n">
         <v>2</v>
@@ -70148,7 +70148,7 @@
         <v>0</v>
       </c>
       <c r="BF144" t="n">
-        <v>-1</v>
+        <v>11303</v>
       </c>
       <c r="BG144" t="n">
         <v>2</v>
@@ -70620,7 +70620,7 @@
         <v>0</v>
       </c>
       <c r="BF145" t="n">
-        <v>-1</v>
+        <v>5290</v>
       </c>
       <c r="BG145" t="n">
         <v>2</v>
@@ -71108,7 +71108,7 @@
         <v>0</v>
       </c>
       <c r="BF146" t="n">
-        <v>-1</v>
+        <v>6852</v>
       </c>
       <c r="BG146" t="n">
         <v>2</v>
@@ -71580,7 +71580,7 @@
         <v>0</v>
       </c>
       <c r="BF147" t="n">
-        <v>-1</v>
+        <v>10541</v>
       </c>
       <c r="BG147" t="n">
         <v>2</v>
@@ -72068,7 +72068,7 @@
         <v>0</v>
       </c>
       <c r="BF148" t="n">
-        <v>-1</v>
+        <v>9583</v>
       </c>
       <c r="BG148" t="n">
         <v>2</v>
@@ -72556,7 +72556,7 @@
         <v>0</v>
       </c>
       <c r="BF149" t="n">
-        <v>-1</v>
+        <v>7890</v>
       </c>
       <c r="BG149" t="n">
         <v>2</v>
@@ -73044,7 +73044,7 @@
         <v>0</v>
       </c>
       <c r="BF150" t="n">
-        <v>-1</v>
+        <v>8431</v>
       </c>
       <c r="BG150" t="n">
         <v>2</v>
@@ -73516,7 +73516,7 @@
         <v>0</v>
       </c>
       <c r="BF151" t="n">
-        <v>-1</v>
+        <v>4058</v>
       </c>
       <c r="BG151" t="n">
         <v>2</v>
@@ -73879,10 +73879,10 @@
         <v>7</v>
       </c>
       <c r="W152" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="X152" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y152" t="n">
         <v>43</v>
@@ -73988,7 +73988,7 @@
         <v>0</v>
       </c>
       <c r="BF152" t="n">
-        <v>-1</v>
+        <v>25512</v>
       </c>
       <c r="BG152" t="n">
         <v>2</v>
@@ -74464,7 +74464,7 @@
         <v>0</v>
       </c>
       <c r="BF153" t="n">
-        <v>-1</v>
+        <v>8394</v>
       </c>
       <c r="BG153" t="n">
         <v>2</v>
@@ -74813,10 +74813,10 @@
         <v>12</v>
       </c>
       <c r="M154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -74865,10 +74865,10 @@
         </is>
       </c>
       <c r="AC154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE154" t="n">
         <v>2.34</v>
@@ -74952,7 +74952,7 @@
         <v>0</v>
       </c>
       <c r="BF154" t="n">
-        <v>-1</v>
+        <v>9053</v>
       </c>
       <c r="BG154" t="n">
         <v>2</v>
@@ -74985,16 +74985,16 @@
         <v>0</v>
       </c>
       <c r="BQ154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS154" t="n">
         <v>1</v>
       </c>
       <c r="BT154" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU154" t="n">
         <v>1</v>
@@ -75440,7 +75440,7 @@
         <v>0</v>
       </c>
       <c r="BF155" t="n">
-        <v>-1</v>
+        <v>3632</v>
       </c>
       <c r="BG155" t="n">
         <v>2</v>
@@ -75912,7 +75912,7 @@
         <v>0</v>
       </c>
       <c r="BF156" t="n">
-        <v>-1</v>
+        <v>3586</v>
       </c>
       <c r="BG156" t="n">
         <v>2</v>
@@ -76400,7 +76400,7 @@
         <v>0</v>
       </c>
       <c r="BF157" t="n">
-        <v>-1</v>
+        <v>8866</v>
       </c>
       <c r="BG157" t="n">
         <v>2</v>
@@ -76888,7 +76888,7 @@
         <v>0</v>
       </c>
       <c r="BF158" t="n">
-        <v>-1</v>
+        <v>9264</v>
       </c>
       <c r="BG158" t="n">
         <v>2</v>
@@ -77376,7 +77376,7 @@
         <v>0</v>
       </c>
       <c r="BF159" t="n">
-        <v>-1</v>
+        <v>10628</v>
       </c>
       <c r="BG159" t="n">
         <v>2</v>
@@ -77848,7 +77848,7 @@
         <v>0</v>
       </c>
       <c r="BF160" t="n">
-        <v>-1</v>
+        <v>4311</v>
       </c>
       <c r="BG160" t="n">
         <v>2</v>
@@ -78336,7 +78336,7 @@
         <v>0</v>
       </c>
       <c r="BF161" t="n">
-        <v>-1</v>
+        <v>6703</v>
       </c>
       <c r="BG161" t="n">
         <v>2</v>
@@ -78816,7 +78816,7 @@
         <v>0</v>
       </c>
       <c r="BF162" t="n">
-        <v>-1</v>
+        <v>9816</v>
       </c>
       <c r="BG162" t="n">
         <v>2</v>
@@ -79304,7 +79304,7 @@
         <v>0</v>
       </c>
       <c r="BF163" t="n">
-        <v>-1</v>
+        <v>8271</v>
       </c>
       <c r="BG163" t="n">
         <v>2</v>
@@ -79784,7 +79784,7 @@
         <v>0</v>
       </c>
       <c r="BF164" t="n">
-        <v>-1</v>
+        <v>10119</v>
       </c>
       <c r="BG164" t="n">
         <v>2</v>
@@ -80256,7 +80256,7 @@
         <v>0</v>
       </c>
       <c r="BF165" t="n">
-        <v>-1</v>
+        <v>11303</v>
       </c>
       <c r="BG165" t="n">
         <v>2</v>
@@ -80744,7 +80744,7 @@
         <v>0</v>
       </c>
       <c r="BF166" t="n">
-        <v>-1</v>
+        <v>11806</v>
       </c>
       <c r="BG166" t="n">
         <v>2</v>
@@ -81224,7 +81224,7 @@
         <v>0</v>
       </c>
       <c r="BF167" t="n">
-        <v>-1</v>
+        <v>6908</v>
       </c>
       <c r="BG167" t="n">
         <v>2</v>
@@ -81712,7 +81712,7 @@
         <v>0</v>
       </c>
       <c r="BF168" t="n">
-        <v>-1</v>
+        <v>9500</v>
       </c>
       <c r="BG168" t="n">
         <v>2</v>
@@ -82200,7 +82200,7 @@
         <v>0</v>
       </c>
       <c r="BF169" t="n">
-        <v>-1</v>
+        <v>5588</v>
       </c>
       <c r="BG169" t="n">
         <v>2</v>
@@ -82672,7 +82672,7 @@
         <v>0</v>
       </c>
       <c r="BF170" t="n">
-        <v>-1</v>
+        <v>2389</v>
       </c>
       <c r="BG170" t="n">
         <v>2</v>
@@ -83160,7 +83160,7 @@
         <v>0</v>
       </c>
       <c r="BF171" t="n">
-        <v>-1</v>
+        <v>6965</v>
       </c>
       <c r="BG171" t="n">
         <v>2</v>
@@ -83632,7 +83632,7 @@
         <v>0</v>
       </c>
       <c r="BF172" t="n">
-        <v>-1</v>
+        <v>11316</v>
       </c>
       <c r="BG172" t="n">
         <v>2</v>
@@ -84003,10 +84003,10 @@
         <v>13</v>
       </c>
       <c r="W173" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="X173" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Y173" t="n">
         <v>48</v>
@@ -84112,7 +84112,7 @@
         <v>0</v>
       </c>
       <c r="BF173" t="n">
-        <v>-1</v>
+        <v>9251</v>
       </c>
       <c r="BG173" t="n">
         <v>2</v>
@@ -84584,7 +84584,7 @@
         <v>0</v>
       </c>
       <c r="BF174" t="n">
-        <v>-1</v>
+        <v>4956</v>
       </c>
       <c r="BG174" t="n">
         <v>2</v>
@@ -85064,7 +85064,7 @@
         <v>0</v>
       </c>
       <c r="BF175" t="n">
-        <v>-1</v>
+        <v>10001</v>
       </c>
       <c r="BG175" t="n">
         <v>2</v>
@@ -85552,7 +85552,7 @@
         <v>0</v>
       </c>
       <c r="BF176" t="n">
-        <v>-1</v>
+        <v>5002</v>
       </c>
       <c r="BG176" t="n">
         <v>2</v>
@@ -85901,7 +85901,7 @@
         <v>9</v>
       </c>
       <c r="M177" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N177" t="n">
         <v>3</v>
@@ -85910,7 +85910,7 @@
         <v>0</v>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q177" t="n">
         <v>4</v>
@@ -85953,10 +85953,10 @@
         </is>
       </c>
       <c r="AC177" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD177" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE177" t="n">
         <v>1.93</v>
@@ -86040,7 +86040,7 @@
         <v>0</v>
       </c>
       <c r="BF177" t="n">
-        <v>-1</v>
+        <v>24716</v>
       </c>
       <c r="BG177" t="n">
         <v>2</v>
@@ -86067,19 +86067,19 @@
         <v>4</v>
       </c>
       <c r="BO177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP177" t="n">
         <v>1</v>
       </c>
       <c r="BQ177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT177" t="n">
         <v>3</v>
@@ -86512,7 +86512,7 @@
         <v>0</v>
       </c>
       <c r="BF178" t="n">
-        <v>-1</v>
+        <v>11561</v>
       </c>
       <c r="BG178" t="n">
         <v>2</v>
@@ -87000,7 +87000,7 @@
         <v>0</v>
       </c>
       <c r="BF179" t="n">
-        <v>-1</v>
+        <v>7057</v>
       </c>
       <c r="BG179" t="n">
         <v>2</v>
@@ -87488,7 +87488,7 @@
         <v>0</v>
       </c>
       <c r="BF180" t="n">
-        <v>-1</v>
+        <v>32506</v>
       </c>
       <c r="BG180" t="n">
         <v>2</v>
@@ -87964,7 +87964,7 @@
         <v>0</v>
       </c>
       <c r="BF181" t="n">
-        <v>-1</v>
+        <v>11265</v>
       </c>
       <c r="BG181" t="n">
         <v>2</v>

--- a/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
+++ b/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
@@ -91788,7 +91788,7 @@
         <v>0</v>
       </c>
       <c r="BF189" t="n">
-        <v>-1</v>
+        <v>10009</v>
       </c>
       <c r="BG189" t="n">
         <v>2</v>
@@ -92764,7 +92764,7 @@
         <v>0</v>
       </c>
       <c r="BF191" t="n">
-        <v>-1</v>
+        <v>6847</v>
       </c>
       <c r="BG191" t="n">
         <v>2</v>

--- a/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
+++ b/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
@@ -93732,7 +93732,7 @@
         <v>0</v>
       </c>
       <c r="BF193" t="n">
-        <v>-1</v>
+        <v>5460</v>
       </c>
       <c r="BG193" t="n">
         <v>2</v>
@@ -94204,7 +94204,7 @@
         <v>0</v>
       </c>
       <c r="BF194" t="n">
-        <v>-1</v>
+        <v>6332</v>
       </c>
       <c r="BG194" t="n">
         <v>2</v>
@@ -94692,7 +94692,7 @@
         <v>0</v>
       </c>
       <c r="BF195" t="n">
-        <v>-1</v>
+        <v>8897</v>
       </c>
       <c r="BG195" t="n">
         <v>2</v>
@@ -95164,7 +95164,7 @@
         <v>0</v>
       </c>
       <c r="BF196" t="n">
-        <v>-1</v>
+        <v>5670</v>
       </c>
       <c r="BG196" t="n">
         <v>2</v>
@@ -95636,7 +95636,7 @@
         <v>0</v>
       </c>
       <c r="BF197" t="n">
-        <v>-1</v>
+        <v>9000</v>
       </c>
       <c r="BG197" t="n">
         <v>2</v>
@@ -96124,7 +96124,7 @@
         <v>0</v>
       </c>
       <c r="BF198" t="n">
-        <v>-1</v>
+        <v>7745</v>
       </c>
       <c r="BG198" t="n">
         <v>2</v>
@@ -96612,7 +96612,7 @@
         <v>0</v>
       </c>
       <c r="BF199" t="n">
-        <v>-1</v>
+        <v>8429</v>
       </c>
       <c r="BG199" t="n">
         <v>2</v>
@@ -97072,7 +97072,7 @@
         <v>0</v>
       </c>
       <c r="BF200" t="n">
-        <v>-1</v>
+        <v>6851</v>
       </c>
       <c r="BG200" t="n">
         <v>2</v>
@@ -97560,7 +97560,7 @@
         <v>0</v>
       </c>
       <c r="BF201" t="n">
-        <v>-1</v>
+        <v>24745</v>
       </c>
       <c r="BG201" t="n">
         <v>2</v>

--- a/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
+++ b/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
@@ -98524,7 +98524,7 @@
         <v>0</v>
       </c>
       <c r="BF203" t="n">
-        <v>-1</v>
+        <v>10706</v>
       </c>
       <c r="BG203" t="n">
         <v>2</v>
@@ -99012,7 +99012,7 @@
         <v>0</v>
       </c>
       <c r="BF204" t="n">
-        <v>-1</v>
+        <v>10826</v>
       </c>
       <c r="BG204" t="n">
         <v>2</v>
@@ -99972,7 +99972,7 @@
         <v>0</v>
       </c>
       <c r="BF206" t="n">
-        <v>-1</v>
+        <v>4713</v>
       </c>
       <c r="BG206" t="n">
         <v>2</v>
@@ -100086,10 +100086,10 @@
         <v>1</v>
       </c>
       <c r="CR206" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CS206" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CT206" t="n">
         <v>1</v>
@@ -100452,7 +100452,7 @@
         <v>0</v>
       </c>
       <c r="BF207" t="n">
-        <v>-1</v>
+        <v>7486</v>
       </c>
       <c r="BG207" t="n">
         <v>2</v>
@@ -100940,7 +100940,7 @@
         <v>0</v>
       </c>
       <c r="BF208" t="n">
-        <v>-1</v>
+        <v>13803</v>
       </c>
       <c r="BG208" t="n">
         <v>2</v>
@@ -101412,7 +101412,7 @@
         <v>0</v>
       </c>
       <c r="BF209" t="n">
-        <v>-1</v>
+        <v>8712</v>
       </c>
       <c r="BG209" t="n">
         <v>2</v>
@@ -101529,7 +101529,7 @@
         <v>14</v>
       </c>
       <c r="CS209" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CT209" t="n">
         <v>1</v>
@@ -101740,7 +101740,7 @@
         </is>
       </c>
       <c r="F210" s="2" t="n">
-        <v>46047.58333333334</v>
+        <v>46047.64583333334</v>
       </c>
       <c r="G210" t="n">
         <v>3</v>
@@ -101900,7 +101900,7 @@
         <v>0</v>
       </c>
       <c r="BF210" t="n">
-        <v>-1</v>
+        <v>3570</v>
       </c>
       <c r="BG210" t="n">
         <v>2</v>
@@ -102380,7 +102380,7 @@
         <v>0</v>
       </c>
       <c r="BF211" t="n">
-        <v>-1</v>
+        <v>8290</v>
       </c>
       <c r="BG211" t="n">
         <v>2</v>

--- a/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
+++ b/data/matches/leagues/Italy_Serie_B_2025-2026.xlsx
@@ -99612,7 +99612,7 @@
         <v>0</v>
       </c>
       <c r="BF212" t="n">
-        <v>-1</v>
+        <v>10636</v>
       </c>
       <c r="BG212" t="n">
         <v>2</v>
@@ -99936,13 +99936,13 @@
         <v>3</v>
       </c>
       <c r="J213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K213" t="n">
         <v>3</v>
       </c>
       <c r="L213" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M213" t="n">
         <v>4</v>
@@ -100909,10 +100909,10 @@
         <v>20</v>
       </c>
       <c r="Y215" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Z215" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
@@ -102288,7 +102288,7 @@
         <v>4</v>
       </c>
       <c r="R218" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S218" t="n">
         <v>8</v>
@@ -102300,7 +102300,7 @@
         <v>12</v>
       </c>
       <c r="V218" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W218" t="n">
         <v>25</v>
@@ -102475,10 +102475,10 @@
         <v>1.25</v>
       </c>
       <c r="CA218" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="CB218" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="CC218" t="n">
         <v>0</v>
@@ -102535,7 +102535,7 @@
         <v>1</v>
       </c>
       <c r="CU218" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CV218" t="n">
         <v>24</v>
@@ -102544,7 +102544,7 @@
         <v>1</v>
       </c>
       <c r="CX218" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY218" t="n">
         <v>8</v>
@@ -102884,7 +102884,7 @@
         <v>0</v>
       </c>
       <c r="BF219" t="n">
-        <v>-1</v>
+        <v>23112</v>
       </c>
       <c r="BG219" t="n">
         <v>2</v>
@@ -103356,7 +103356,7 @@
         <v>0</v>
       </c>
       <c r="BF220" t="n">
-        <v>-1</v>
+        <v>7702</v>
       </c>
       <c r="BG220" t="n">
         <v>2</v>
@@ -103717,10 +103717,10 @@
         <v>9</v>
       </c>
       <c r="Y221" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Z221" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
@@ -103820,7 +103820,7 @@
         <v>0</v>
       </c>
       <c r="BF221" t="n">
-        <v>-1</v>
+        <v>7134</v>
       </c>
       <c r="BG221" t="n">
         <v>2</v>
